--- a/tests/test_convert/testing_files/main_dir/mwtab_nmr_conversion_directives_compare.xlsx
+++ b/tests/test_convert/testing_files/main_dir/mwtab_nmr_conversion_directives_compare.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="142">
   <si>
     <t>#tags</t>
   </si>
@@ -277,7 +277,7 @@
     <t>;</t>
   </si>
   <si>
-    <t>NM</t>
+    <t>NMR</t>
   </si>
   <si>
     <t>acquisition_time," ",acquisition_time%units</t>
@@ -358,6 +358,36 @@
     <t>False</t>
   </si>
   <si>
+    <t>#.fill_headers</t>
+  </si>
+  <si>
+    <t>#.fields_to_headers</t>
+  </si>
+  <si>
+    <t>#.table</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>study</t>
+  </si>
+  <si>
+    <t>entity</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>protocol</t>
+  </si>
+  <si>
+    <t>#.for_each</t>
+  </si>
+  <si>
+    <t>measurement</t>
+  </si>
+  <si>
     <t>*#.headers</t>
   </si>
   <si>
@@ -367,31 +397,16 @@
     <t>"Metabolite"=assignment</t>
   </si>
   <si>
-    <t>#.fields_to_headers</t>
-  </si>
-  <si>
-    <t>#.table</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>study</t>
-  </si>
-  <si>
-    <t>entity</t>
-  </si>
-  <si>
-    <t>section</t>
-  </si>
-  <si>
-    <t>protocol</t>
-  </si>
-  <si>
-    <t>#.for_each</t>
-  </si>
-  <si>
-    <t>measurement</t>
+    <t>#.test</t>
+  </si>
+  <si>
+    <t>type=subject</t>
+  </si>
+  <si>
+    <t>type=collection</t>
+  </si>
+  <si>
+    <t>machine_type=NMR</t>
   </si>
   <si>
     <t>*#.optional_headers</t>
@@ -403,18 +418,6 @@
     <t>"Metabolite"=assignment,"sample_id"=entity.id</t>
   </si>
   <si>
-    <t>#.test</t>
-  </si>
-  <si>
-    <t>type=subject</t>
-  </si>
-  <si>
-    <t>type=collection</t>
-  </si>
-  <si>
-    <t>machine_type=NMR</t>
-  </si>
-  <si>
     <t>*#.sort_by</t>
   </si>
   <si>
@@ -427,13 +430,13 @@
     <t>ascending</t>
   </si>
   <si>
+    <t>type=treatment</t>
+  </si>
+  <si>
+    <t>type=sample_prep</t>
+  </si>
+  <si>
     <t>matrix</t>
-  </si>
-  <si>
-    <t>type=treatment</t>
-  </si>
-  <si>
-    <t>type=sample_prep</t>
   </si>
   <si>
     <t>#.values_to_str</t>
@@ -768,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -857,7 +860,7 @@
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F9" t="s">
         <v>109</v>
@@ -874,7 +877,7 @@
         <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
         <v>110</v>
@@ -891,7 +894,7 @@
         <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
         <v>110</v>
@@ -908,7 +911,7 @@
         <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F12" t="s">
         <v>110</v>
@@ -925,7 +928,7 @@
         <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F13" t="s">
         <v>110</v>
@@ -942,7 +945,7 @@
         <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
         <v>110</v>
@@ -959,7 +962,7 @@
         <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F15" t="s">
         <v>110</v>
@@ -976,7 +979,7 @@
         <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F16" t="s">
         <v>110</v>
@@ -993,7 +996,7 @@
         <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
         <v>110</v>
@@ -1010,7 +1013,7 @@
         <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s">
         <v>110</v>
@@ -1030,7 +1033,7 @@
         <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F20" t="s">
         <v>109</v>
@@ -1047,7 +1050,7 @@
         <v>112</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F21" t="s">
         <v>110</v>
@@ -1064,7 +1067,7 @@
         <v>112</v>
       </c>
       <c r="E22" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F22" t="s">
         <v>110</v>
@@ -1081,7 +1084,7 @@
         <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F23" t="s">
         <v>110</v>
@@ -1098,7 +1101,7 @@
         <v>112</v>
       </c>
       <c r="E24" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
         <v>110</v>
@@ -1115,7 +1118,7 @@
         <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
         <v>110</v>
@@ -1132,7 +1135,7 @@
         <v>112</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
         <v>110</v>
@@ -1149,7 +1152,7 @@
         <v>112</v>
       </c>
       <c r="E27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
         <v>110</v>
@@ -1166,7 +1169,7 @@
         <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s">
         <v>110</v>
@@ -1183,7 +1186,7 @@
         <v>112</v>
       </c>
       <c r="E29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s">
         <v>110</v>
@@ -1203,10 +1206,10 @@
         <v>111</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G31" t="s">
         <v>109</v>
@@ -1223,10 +1226,10 @@
         <v>112</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G32" t="s">
         <v>110</v>
@@ -1243,10 +1246,10 @@
         <v>112</v>
       </c>
       <c r="E33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G33" t="s">
         <v>110</v>
@@ -1263,10 +1266,10 @@
         <v>112</v>
       </c>
       <c r="E34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G34" t="s">
         <v>110</v>
@@ -1300,7 +1303,7 @@
         <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1317,10 +1320,10 @@
         <v>111</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G39" t="s">
         <v>109</v>
@@ -1337,10 +1340,10 @@
         <v>113</v>
       </c>
       <c r="E40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G40" t="s">
         <v>110</v>
@@ -1357,10 +1360,10 @@
         <v>112</v>
       </c>
       <c r="E41" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F41" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G41" t="s">
         <v>110</v>
@@ -1377,10 +1380,10 @@
         <v>112</v>
       </c>
       <c r="E42" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F42" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G42" t="s">
         <v>110</v>
@@ -1397,10 +1400,10 @@
         <v>112</v>
       </c>
       <c r="E43" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F43" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G43" t="s">
         <v>110</v>
@@ -1420,22 +1423,22 @@
         <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F45" t="s">
         <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I45" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J45" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K45" t="s">
         <v>109</v>
@@ -1461,10 +1464,10 @@
         <v>83</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J46" t="s">
         <v>138</v>
@@ -1493,10 +1496,10 @@
         <v>83</v>
       </c>
       <c r="H47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J47" t="s">
         <v>138</v>
@@ -1525,10 +1528,10 @@
         <v>83</v>
       </c>
       <c r="H48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J48" t="s">
         <v>138</v>
@@ -1551,22 +1554,22 @@
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F50" t="s">
         <v>111</v>
       </c>
       <c r="G50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I50" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K50" t="s">
         <v>109</v>
@@ -1589,13 +1592,13 @@
         <v>113</v>
       </c>
       <c r="G51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H51" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J51" t="s">
         <v>139</v>
@@ -1621,13 +1624,13 @@
         <v>112</v>
       </c>
       <c r="G52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J52" t="s">
         <v>139</v>
@@ -1653,13 +1656,13 @@
         <v>112</v>
       </c>
       <c r="G53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H53" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I53" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J53" t="s">
         <v>139</v>
@@ -1707,10 +1710,10 @@
         <v>111</v>
       </c>
       <c r="E58" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G58" t="s">
         <v>109</v>
@@ -1727,10 +1730,10 @@
         <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F59" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G59" t="s">
         <v>110</v>
@@ -1747,10 +1750,10 @@
         <v>113</v>
       </c>
       <c r="E60" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F60" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G60" t="s">
         <v>110</v>
@@ -1767,10 +1770,10 @@
         <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F61" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G61" t="s">
         <v>110</v>
@@ -1787,10 +1790,10 @@
         <v>112</v>
       </c>
       <c r="E62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F62" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G62" t="s">
         <v>110</v>
@@ -1807,10 +1810,10 @@
         <v>112</v>
       </c>
       <c r="E63" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F63" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G63" t="s">
         <v>110</v>
@@ -1827,16 +1830,16 @@
         <v>112</v>
       </c>
       <c r="E64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F64" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G64" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:11">
       <c r="B65" t="s">
         <v>47</v>
       </c>
@@ -1847,16 +1850,16 @@
         <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F65" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G65" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:11">
       <c r="B66" t="s">
         <v>48</v>
       </c>
@@ -1867,16 +1870,16 @@
         <v>113</v>
       </c>
       <c r="E66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F66" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G66" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:11">
       <c r="B67" t="s">
         <v>49</v>
       </c>
@@ -1887,16 +1890,16 @@
         <v>113</v>
       </c>
       <c r="E67" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F67" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G67" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:11">
       <c r="B68" t="s">
         <v>50</v>
       </c>
@@ -1907,16 +1910,16 @@
         <v>113</v>
       </c>
       <c r="E68" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F68" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G68" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:11">
       <c r="B69" t="s">
         <v>51</v>
       </c>
@@ -1927,16 +1930,16 @@
         <v>113</v>
       </c>
       <c r="E69" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F69" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G69" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:11">
       <c r="B70" t="s">
         <v>52</v>
       </c>
@@ -1947,16 +1950,16 @@
         <v>113</v>
       </c>
       <c r="E70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F70" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G70" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:11">
       <c r="B71" t="s">
         <v>53</v>
       </c>
@@ -1967,16 +1970,16 @@
         <v>112</v>
       </c>
       <c r="E71" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F71" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G71" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:11">
       <c r="B72" t="s">
         <v>54</v>
       </c>
@@ -1987,16 +1990,16 @@
         <v>113</v>
       </c>
       <c r="E72" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F72" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G72" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:11">
       <c r="B73" t="s">
         <v>55</v>
       </c>
@@ -2007,16 +2010,16 @@
         <v>113</v>
       </c>
       <c r="E73" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F73" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G73" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:11">
       <c r="B74" t="s">
         <v>56</v>
       </c>
@@ -2027,16 +2030,16 @@
         <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F74" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G74" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -2050,13 +2053,13 @@
         <v>111</v>
       </c>
       <c r="E76" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F76" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:11">
       <c r="B77" t="s">
         <v>58</v>
       </c>
@@ -2067,13 +2070,13 @@
         <v>112</v>
       </c>
       <c r="E77" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F77" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -2087,54 +2090,57 @@
         <v>114</v>
       </c>
       <c r="E79" t="s">
+        <v>124</v>
+      </c>
+      <c r="F79" t="s">
         <v>111</v>
       </c>
-      <c r="F79" t="s">
-        <v>133</v>
-      </c>
       <c r="G79" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H79" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="I79" t="s">
+        <v>116</v>
+      </c>
+      <c r="J79" t="s">
         <v>109</v>
       </c>
-      <c r="J79" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="K79" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="B80" t="s">
         <v>59</v>
       </c>
       <c r="C80" t="s">
         <v>106</v>
       </c>
-      <c r="D80" t="s">
-        <v>115</v>
-      </c>
       <c r="E80" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F80" t="s">
+        <v>112</v>
+      </c>
+      <c r="G80" t="s">
         <v>106</v>
       </c>
-      <c r="G80" t="s">
-        <v>136</v>
-      </c>
       <c r="H80" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="J80" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
+        <v>140</v>
+      </c>
+      <c r="K80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
         <v>0</v>
       </c>
@@ -2148,60 +2154,63 @@
         <v>114</v>
       </c>
       <c r="E82" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F82" t="s">
+        <v>131</v>
+      </c>
+      <c r="G82" t="s">
         <v>111</v>
       </c>
-      <c r="G82" t="s">
-        <v>133</v>
-      </c>
       <c r="H82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I82" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J82" t="s">
+        <v>116</v>
+      </c>
+      <c r="K82" t="s">
         <v>109</v>
       </c>
-      <c r="K82" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+      <c r="L82" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="B83" t="s">
         <v>60</v>
       </c>
       <c r="C83" t="s">
         <v>106</v>
       </c>
-      <c r="D83" t="s">
-        <v>116</v>
-      </c>
       <c r="E83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F83" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="G83" t="s">
+        <v>112</v>
+      </c>
+      <c r="H83" t="s">
         <v>106</v>
       </c>
-      <c r="H83" t="s">
-        <v>136</v>
-      </c>
       <c r="I83" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="J83" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K83" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
+        <v>140</v>
+      </c>
+      <c r="L83" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
         <v>0</v>
       </c>
@@ -2212,31 +2221,34 @@
         <v>107</v>
       </c>
       <c r="D85" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
+        <v>124</v>
+      </c>
+      <c r="G85" t="s">
         <v>111</v>
       </c>
-      <c r="G85" t="s">
-        <v>133</v>
-      </c>
       <c r="H85" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I85" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J85" t="s">
+        <v>116</v>
+      </c>
+      <c r="K85" t="s">
         <v>109</v>
       </c>
-      <c r="K85" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="L85" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="B86" t="s">
         <v>61</v>
       </c>
@@ -2246,25 +2258,25 @@
       <c r="D86" t="s">
         <v>112</v>
       </c>
-      <c r="E86" t="s">
-        <v>128</v>
-      </c>
       <c r="F86" t="s">
+        <v>133</v>
+      </c>
+      <c r="G86" t="s">
         <v>113</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>106</v>
       </c>
-      <c r="H86" t="s">
-        <v>136</v>
-      </c>
       <c r="I86" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="J86" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="K86" t="s">
+        <v>140</v>
+      </c>
+      <c r="L86" t="s">
         <v>112</v>
       </c>
     </row>
